--- a/slide_classification/TCGA_Results/Caption_based_aggregation/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -755,16 +755,16 @@
         <v>0.8543689320388349</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8762886597938144</v>
+        <v>0.865979381443299</v>
       </c>
       <c r="D14" t="n">
         <v>0.8392857142857143</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8712871287128713</v>
+        <v>0.8910891089108911</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8603076087078088</v>
+        <v>0.8626807841696849</v>
       </c>
     </row>
     <row r="15">
@@ -777,16 +777,16 @@
         <v>0.6106060606060606</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5</v>
       </c>
       <c r="D15" t="n">
         <v>0.5891304347826087</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5664794007490637</v>
+        <v>0.6137640449438202</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5761693586498179</v>
+        <v>0.5783751350831223</v>
       </c>
     </row>
     <row r="16">
@@ -799,16 +799,16 @@
         <v>0.6329294369208838</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5380952380952381</v>
+        <v>0.4640883977900552</v>
       </c>
       <c r="D16" t="n">
         <v>0.6083916083916083</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5825119236883943</v>
+        <v>0.6467408585055644</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5904820517740311</v>
+        <v>0.5880375754020279</v>
       </c>
     </row>
     <row r="17">
@@ -821,16 +821,16 @@
         <v>0.8349929762160143</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8273932253313697</v>
+        <v>0.8037819673064874</v>
       </c>
       <c r="D17" t="n">
         <v>0.8016983016983018</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8472225282941649</v>
+        <v>0.8707267547104471</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8278267578849626</v>
+        <v>0.8277999999828127</v>
       </c>
     </row>
     <row r="18">
@@ -843,16 +843,16 @@
         <v>0.7390151515151515</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6822344322344321</v>
+        <v>0.7280219780219781</v>
       </c>
       <c r="D18" t="n">
         <v>0.6459239130434783</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6577715355805243</v>
+        <v>0.7102059925093633</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6812362580933966</v>
+        <v>0.7057917587724928</v>
       </c>
     </row>
     <row r="19">
@@ -868,7 +868,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[84, 0], [12, 1]]</t>
+          <t>[[84, 0], [13, 0]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[86, 3], [10, 2]]</t>
+          <t>[[87, 2], [9, 3]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1406,34 +1406,34 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8603076087078088</v>
+        <v>0.8626807841696849</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01460420982993766</v>
+        <v>0.01893627365201709</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5761693586498179</v>
+        <v>0.5783751350831223</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02678456142824209</v>
+        <v>0.04623187691441166</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5904820517740311</v>
+        <v>0.5880375754020279</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03510852429667717</v>
+        <v>0.07286809996045486</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8278267578849626</v>
+        <v>0.8277999999828127</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01666159332197904</v>
+        <v>0.02807405263546108</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6812362580933966</v>
+        <v>0.7057917587724928</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03583626582175149</v>
+        <v>0.03606113172423302</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -613,7 +613,7 @@
         <v>0.7475728155339806</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7938144329896907</v>
+        <v>0.7525773195876289</v>
       </c>
       <c r="D8" t="n">
         <v>0.75</v>
@@ -622,7 +622,7 @@
         <v>0.7821782178217822</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7683913665863633</v>
+        <v>0.7580820882358479</v>
       </c>
     </row>
     <row r="9">
@@ -635,7 +635,7 @@
         <v>0.7693181818181818</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6208791208791209</v>
+        <v>0.6295787545787546</v>
       </c>
       <c r="D9" t="n">
         <v>0.7304347826086957</v>
@@ -644,7 +644,7 @@
         <v>0.6601123595505618</v>
       </c>
       <c r="F9" t="n">
-        <v>0.69518611121414</v>
+        <v>0.6973610196390485</v>
       </c>
     </row>
     <row r="10">
@@ -657,7 +657,7 @@
         <v>0.6566666666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6056910569105691</v>
+        <v>0.5907172995780591</v>
       </c>
       <c r="D10" t="n">
         <v>0.6666666666666667</v>
@@ -666,7 +666,7 @@
         <v>0.6109943977591037</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6350046970007516</v>
+        <v>0.631261257667624</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +679,7 @@
         <v>0.7818770226537218</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8050456793227725</v>
+        <v>0.7791117490973943</v>
       </c>
       <c r="D11" t="n">
         <v>0.7738095238095238</v>
@@ -688,7 +688,7 @@
         <v>0.8077280417117343</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7921150668744381</v>
+        <v>0.7856315843180937</v>
       </c>
     </row>
     <row r="12">
@@ -701,16 +701,16 @@
         <v>0.8401515151515152</v>
       </c>
       <c r="C12" t="n">
-        <v>0.836996336996337</v>
+        <v>0.8177655677655677</v>
       </c>
       <c r="D12" t="n">
         <v>0.8347826086956521</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6928838951310862</v>
+        <v>0.7565543071161049</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8012035889936476</v>
+        <v>0.81231349968221</v>
       </c>
     </row>
     <row r="13">
@@ -726,7 +726,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[72, 12], [8, 5]]</t>
+          <t>[[67, 17], [7, 6]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[70, 18], [6, 9]]</t>
+          <t>[[69, 20], [6, 10]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7683913665863633</v>
+        <v>0.7580820882358479</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02005033668776058</v>
+        <v>0.01402400532896004</v>
       </c>
       <c r="H3" t="n">
-        <v>0.69518611121414</v>
+        <v>0.6973610196390485</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05807264759663317</v>
+        <v>0.05534800159205855</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6350046970007516</v>
+        <v>0.631261257667624</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0269606436215022</v>
+        <v>0.03143857479641103</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7921150668744381</v>
+        <v>0.7856315843180937</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01458489096570349</v>
+        <v>0.0130826175574109</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8012035889936476</v>
+        <v>0.81231349968221</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06256750035803206</v>
+        <v>0.0332363828023477</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[70, 18], [6, 9]]</t>
+          <t>[[69, 20], [6, 10]]</t>
         </is>
       </c>
     </row>
